--- a/data/news.xlsx
+++ b/data/news.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar-new/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E05BA559-CE63-864F-A7A7-0FDDE6A5EBE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A0BAFC-76ED-114B-ADD4-064B1151DE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3700" windowWidth="38400" windowHeight="20040" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -46,9 +46,6 @@
     <t>Starting my PhD at Harvard Engineering!</t>
   </si>
   <si>
-    <t>assets/images/news/Harvard_SEC.jpg</t>
-  </si>
-  <si>
     <t>July</t>
   </si>
   <si>
@@ -64,9 +61,6 @@
     <t>Honored to be selected as a GEM Associate Fellow!</t>
   </si>
   <si>
-    <t>assets/images/news/GEM.png</t>
-  </si>
-  <si>
     <t>May</t>
   </si>
   <si>
@@ -115,9 +109,6 @@
     <t>After an incredibly fun year and a half, it’s time to say goodbye. It has been an inspiring place to learn, build, and grow. Going to miss the people here!</t>
   </si>
   <si>
-    <t>assets/images/news/HAMR_Goodbye_Dinner.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -133,22 +124,31 @@
     <t>Organized the first Hopkins-India Conference in Washington DC!</t>
   </si>
   <si>
-    <t>assets/images/news/JH_India_Conference.jpg</t>
-  </si>
-  <si>
-    <t>assets/images/news/NDSEG.png</t>
-  </si>
-  <si>
     <t xml:space="preserve">Excited to be nominated for six years of tuition coverage, and three years of stipend coverage from Harvard SEAS! </t>
   </si>
   <si>
     <t>Thrilled to be selected for the NDSEG Fellowship, supporting three years of my tuition and stipend towards my PhD!</t>
   </si>
   <si>
-    <t>assets/images/news/ICORR.jpg</t>
-  </si>
-  <si>
     <t>Two down, one to go!</t>
+  </si>
+  <si>
+    <t>/assets/images/news/Harvard_SEC.jpg</t>
+  </si>
+  <si>
+    <t>/assets/images/news/HAMR_Goodbye_Dinner.jpg</t>
+  </si>
+  <si>
+    <t>/assets/images/news/GEM.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/ICORR.jpg</t>
+  </si>
+  <si>
+    <t>/assets/images/news/JH_India_Conference.jpg</t>
+  </si>
+  <si>
+    <t>/assets/images/news/NDSEG.png</t>
   </si>
 </sst>
 </file>
@@ -700,7 +700,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -720,16 +720,13 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1135,7 +1132,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -1164,10 +1161,10 @@
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
@@ -1175,46 +1172,46 @@
       <c r="J2" s="7"/>
       <c r="K2" s="7"/>
       <c r="L2" s="9"/>
-      <c r="M2" s="10"/>
+      <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2025</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>10</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H3" s="8"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="9"/>
-      <c r="M3" s="10"/>
+      <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="76" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="57" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2025</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -1223,23 +1220,22 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="10"/>
     </row>
     <row r="5" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2025</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -1248,23 +1244,23 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9"/>
-      <c r="M5" s="10"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2025</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -1273,20 +1269,20 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="10"/>
+      <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2025</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" s="7" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
@@ -1296,23 +1292,22 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="9"/>
-      <c r="M7" s="10"/>
     </row>
     <row r="8" spans="1:13" ht="38" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2025</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -1321,23 +1316,22 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="9"/>
-      <c r="M8" s="10"/>
     </row>
     <row r="9" spans="1:13" ht="38" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>2025</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -1346,20 +1340,19 @@
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="9"/>
-      <c r="M9" s="10"/>
     </row>
     <row r="10" spans="1:13" ht="38" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2025</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -1369,17 +1362,16 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="9"/>
-      <c r="M10" s="10"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>2024</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -1390,7 +1382,6 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="9"/>
-      <c r="M11" s="10"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
@@ -1400,39 +1391,27 @@
         <v>6</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>2024</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
@@ -1442,22 +1421,16 @@
         <v>6</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9"/>
       <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
     </row>
     <row r="19" spans="3:3" ht="20" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/data/news.xlsx
+++ b/data/news.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A0BAFC-76ED-114B-ADD4-064B1151DE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9992C0C3-978A-F848-A185-C98D47D22AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17820" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="-38400" yWindow="-3720" windowWidth="38400" windowHeight="21120" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>year</t>
   </si>
@@ -46,12 +46,6 @@
     <t>Starting my PhD at Harvard Engineering!</t>
   </si>
   <si>
-    <t>July</t>
-  </si>
-  <si>
-    <t>Had an amazing time home in Pune, charged.</t>
-  </si>
-  <si>
     <t>June</t>
   </si>
   <si>
@@ -95,9 +89,6 @@
   </si>
   <si>
     <t>Starting my Master's in BME at Johns Hopkins!</t>
-  </si>
-  <si>
-    <t>unfiltered;</t>
   </si>
   <si>
     <t>body</t>
@@ -1104,14 +1095,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36804C05-0050-DB4A-B44D-23DEA2DFD96A}">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="68.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="71.1640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="40.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="54.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="59.1640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="14.83203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="80.83203125" style="1" customWidth="1"/>
@@ -1132,7 +1123,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -1161,10 +1152,10 @@
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
@@ -1174,7 +1165,7 @@
       <c r="L2" s="9"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="57" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2025</v>
       </c>
@@ -1184,34 +1175,35 @@
       <c r="C3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
+      <c r="D3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>35</v>
+      </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="G3" s="7"/>
       <c r="H3" s="8"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="9"/>
-      <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="57" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2025</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>11</v>
-      </c>
       <c r="D4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -1220,22 +1212,23 @@
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="9"/>
+      <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2025</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -1246,22 +1239,20 @@
       <c r="L5" s="9"/>
       <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2025</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>14</v>
-      </c>
       <c r="D6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>40</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="8"/>
@@ -1269,22 +1260,23 @@
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="38" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2025</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="7"/>
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="8"/>
@@ -1298,16 +1290,16 @@
         <v>2025</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
@@ -1328,11 +1320,9 @@
         <v>17</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>42</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="8"/>
@@ -1341,9 +1331,9 @@
       <c r="K9" s="7"/>
       <c r="L9" s="9"/>
     </row>
-    <row r="10" spans="1:13" ht="38" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>18</v>
@@ -1351,9 +1341,7 @@
       <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>34</v>
-      </c>
+      <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -1368,30 +1356,25 @@
         <v>2024</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>2024</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
@@ -1400,37 +1383,22 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
       <c r="G13" s="9"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="19" spans="3:3" ht="20" x14ac:dyDescent="0.25">
-      <c r="C19" s="1" t="s">
-        <v>29</v>
+    <row r="18" spans="3:3" ht="20" x14ac:dyDescent="0.25">
+      <c r="C18" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/news.xlsx
+++ b/data/news.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9992C0C3-978A-F848-A185-C98D47D22AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E411CA5-5B00-7740-A273-7A9AA0370E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3720" windowWidth="38400" windowHeight="21120" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="projects" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
   <si>
     <t>year</t>
   </si>
@@ -49,9 +49,6 @@
     <t>June</t>
   </si>
   <si>
-    <t>Said goodbye to the JH Haptics &amp; Medical Robotics Lab!</t>
-  </si>
-  <si>
     <t>Honored to be selected as a GEM Associate Fellow!</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>Harvard Science and Engineering Center, Allston MA.</t>
   </si>
   <si>
-    <t>After an incredibly fun year and a half, it’s time to say goodbye. It has been an inspiring place to learn, build, and grow. Going to miss the people here!</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -112,9 +106,6 @@
     <t>Helped bring together leaders, researchers, and alumni to build bridges between Hopkins and India!</t>
   </si>
   <si>
-    <t>Organized the first Hopkins-India Conference in Washington DC!</t>
-  </si>
-  <si>
     <t xml:space="preserve">Excited to be nominated for six years of tuition coverage, and three years of stipend coverage from Harvard SEAS! </t>
   </si>
   <si>
@@ -127,9 +118,6 @@
     <t>/assets/images/news/Harvard_SEC.jpg</t>
   </si>
   <si>
-    <t>/assets/images/news/HAMR_Goodbye_Dinner.jpg</t>
-  </si>
-  <si>
     <t>/assets/images/news/GEM.png</t>
   </si>
   <si>
@@ -140,6 +128,12 @@
   </si>
   <si>
     <t>/assets/images/news/NDSEG.png</t>
+  </si>
+  <si>
+    <t>Excited to be able to join Prof. Katia Bertoldi and Prof. Giovanni Traverso for this marathon.</t>
+  </si>
+  <si>
+    <t>Helped organize the first Hopkins-India Conference in Washington DC!</t>
   </si>
 </sst>
 </file>
@@ -1095,7 +1089,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36804C05-0050-DB4A-B44D-23DEA2DFD96A}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="1" customWidth="1"/>
@@ -1123,7 +1117,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -1150,12 +1144,14 @@
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="7" t="s">
+        <v>36</v>
+      </c>
       <c r="E2" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
@@ -1165,7 +1161,7 @@
       <c r="L2" s="9"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" ht="57" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2025</v>
       </c>
@@ -1179,7 +1175,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -1188,22 +1184,23 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="9"/>
+      <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2025</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -1214,22 +1211,20 @@
       <c r="L4" s="9"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2025</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>37</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="8"/>
@@ -1237,22 +1232,23 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9"/>
-      <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="38" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2025</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>34</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="8"/>
@@ -1266,16 +1262,16 @@
         <v>2025</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>29</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -1290,17 +1286,15 @@
         <v>2025</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>39</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="8"/>
@@ -1309,19 +1303,17 @@
       <c r="K8" s="7"/>
       <c r="L8" s="9"/>
     </row>
-    <row r="9" spans="1:13" ht="38" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>31</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="D9" s="7"/>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -1336,27 +1328,22 @@
         <v>2024</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="7">
         <v>2024</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>20</v>
@@ -1368,10 +1355,10 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>21</v>
@@ -1381,24 +1368,9 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="18" spans="3:3" ht="20" x14ac:dyDescent="0.25">
-      <c r="C18" s="1" t="s">
-        <v>26</v>
+    <row r="17" spans="3:3" ht="20" x14ac:dyDescent="0.25">
+      <c r="C17" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/data/news.xlsx
+++ b/data/news.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E411CA5-5B00-7740-A273-7A9AA0370E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87558CD-761D-E142-AD90-BCA9282D6FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>year</t>
   </si>
@@ -97,9 +97,6 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>Grateful to be part of this vibrant community of scholars and engineers.</t>
-  </si>
-  <si>
     <t>Had the chance to share my work on optimizing multimodal feedback at RehabWeek in Chicago. Grateful for the opportunity to present to such a clinically impact-driven audience, and for the really insightful conversations throughout.</t>
   </si>
   <si>
@@ -112,9 +109,6 @@
     <t>Thrilled to be selected for the NDSEG Fellowship, supporting three years of my tuition and stipend towards my PhD!</t>
   </si>
   <si>
-    <t>Two down, one to go!</t>
-  </si>
-  <si>
     <t>/assets/images/news/Harvard_SEC.jpg</t>
   </si>
   <si>
@@ -130,10 +124,13 @@
     <t>/assets/images/news/NDSEG.png</t>
   </si>
   <si>
-    <t>Excited to be able to join Prof. Katia Bertoldi and Prof. Giovanni Traverso for this marathon.</t>
-  </si>
-  <si>
     <t>Helped organize the first Hopkins-India Conference in Washington DC!</t>
+  </si>
+  <si>
+    <t>Grateful to be a part of a vibrant community of scholars and engineers supported through industry partnerships, professional development, and a strong national network.</t>
+  </si>
+  <si>
+    <t>Two down, one more to go!</t>
   </si>
 </sst>
 </file>
@@ -1144,11 +1141,9 @@
       <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>23</v>
@@ -1161,7 +1156,7 @@
       <c r="L2" s="9"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="4" customFormat="1" ht="57" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2025</v>
       </c>
@@ -1172,10 +1167,10 @@
         <v>9</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -1197,10 +1192,10 @@
         <v>11</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -1222,7 +1217,7 @@
         <v>12</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -1241,13 +1236,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -1268,10 +1263,10 @@
         <v>14</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
@@ -1292,7 +1287,7 @@
         <v>16</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>

--- a/data/news.xlsx
+++ b/data/news.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anwaypimpalkar/everything/anwaypimpalkar.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D87558CD-761D-E142-AD90-BCA9282D6FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1FD641-25C9-964F-B396-225FE4E148F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{46DB94BC-6658-C940-A428-5CA04B255DCE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
   <si>
     <t>year</t>
   </si>
@@ -46,54 +46,27 @@
     <t>Starting my PhD at Harvard Engineering!</t>
   </si>
   <si>
-    <t>June</t>
-  </si>
-  <si>
-    <t>Honored to be selected as a GEM Associate Fellow!</t>
-  </si>
-  <si>
     <t>May</t>
   </si>
   <si>
     <t>Presented at ICORR 2025, as a Best Student Paper Finalist!</t>
   </si>
   <si>
-    <t>Graduated from Hopkins with my Master's!</t>
-  </si>
-  <si>
     <t>April</t>
   </si>
   <si>
-    <t>Honored to be awarded in the NDSEG 2025-28 cohort!</t>
-  </si>
-  <si>
-    <t>February</t>
-  </si>
-  <si>
-    <t>I've been nominated for the Harvard SEAS Prize Fellowship!</t>
-  </si>
-  <si>
     <t>October</t>
   </si>
   <si>
     <t>Presented at the BMES Annual Meet 2024!</t>
   </si>
   <si>
-    <t>Wrapped up a fun summer at Harvard SEAS!</t>
-  </si>
-  <si>
     <t>Demo'ed my work at the IEEE Haptics Symposium 2024!</t>
   </si>
   <si>
-    <t>Starting my Master's in BME at Johns Hopkins!</t>
-  </si>
-  <si>
     <t>body</t>
   </si>
   <si>
-    <t>Harvard Science and Engineering Center, Allston MA.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -103,34 +76,67 @@
     <t>Helped bring together leaders, researchers, and alumni to build bridges between Hopkins and India!</t>
   </si>
   <si>
-    <t xml:space="preserve">Excited to be nominated for six years of tuition coverage, and three years of stipend coverage from Harvard SEAS! </t>
-  </si>
-  <si>
-    <t>Thrilled to be selected for the NDSEG Fellowship, supporting three years of my tuition and stipend towards my PhD!</t>
-  </si>
-  <si>
-    <t>/assets/images/news/Harvard_SEC.jpg</t>
-  </si>
-  <si>
-    <t>/assets/images/news/GEM.png</t>
-  </si>
-  <si>
-    <t>/assets/images/news/ICORR.jpg</t>
-  </si>
-  <si>
-    <t>/assets/images/news/JH_India_Conference.jpg</t>
-  </si>
-  <si>
-    <t>/assets/images/news/NDSEG.png</t>
-  </si>
-  <si>
     <t>Helped organize the first Hopkins-India Conference in Washington DC!</t>
   </si>
   <si>
-    <t>Grateful to be a part of a vibrant community of scholars and engineers supported through industry partnerships, professional development, and a strong national network.</t>
-  </si>
-  <si>
-    <t>Two down, one more to go!</t>
+    <t>/assets/images/news/Harvard_SEC.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/JH_Masters_Graduation.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/ICORR.png</t>
+  </si>
+  <si>
+    <t>Thrilled to be selected for the NDSEG Fellowship, which will support three years of tuition and stipend during my PhD. I am also grateful to receive the Harvard SEAS Prize Fellowship, providing six years of tuition support and two years of stipend funding, and to join the GEM Fellowship community, expanding my network of scholars, engineers, and industry partners.</t>
+  </si>
+  <si>
+    <t>/assets/images/news/Fellowships.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/JH_India_Conference.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/NIA_Challenge.png</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>/assets/images/news/BJA_Article.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/BMES.png</t>
+  </si>
+  <si>
+    <t>/assets/images/news/Haptics_Symposium.png</t>
+  </si>
+  <si>
+    <t>Two degrees down, one more to go!</t>
+  </si>
+  <si>
+    <t>Named an NIA Startup Challenge Finalist!</t>
+  </si>
+  <si>
+    <t>We have received a $10,000 prize to continue building Re-Kinesis with Junjun Chen, Ariel Slepyan, Sam Bello, and Nitish Thakor.</t>
+  </si>
+  <si>
+    <t>New study published in the British Journal of Anaesthesia!</t>
+  </si>
+  <si>
+    <t>Excited to contribute to a study showing that AI could predict major postoperative complications more accurately than commonly used clinical risk scores, using information hidden in routine ECGs.</t>
+  </si>
+  <si>
+    <t>Excited to present my work on visual and haptic feedback for stroke rehabilitation and represent Johns Hopkins Biomedical Engineering at the department booth!</t>
+  </si>
+  <si>
+    <t>Excited to demo our Johns Hopkins Haptic Interfaces class project, which was selected as both a live demonstration and a work-in-progress paper. I also joined the conference as a student volunteer!</t>
+  </si>
+  <si>
+    <t>Selected for the NDSEG, Harvard SEAS Prize, and GEM Fellowships!</t>
+  </si>
+  <si>
+    <t>Graduated from Hopkins with my Master's in Biomedical Engineering!</t>
   </si>
 </sst>
 </file>
@@ -682,7 +688,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -709,6 +715,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1086,7 +1098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36804C05-0050-DB4A-B44D-23DEA2DFD96A}">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="1" customWidth="1"/>
@@ -1114,7 +1126,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -1143,11 +1155,9 @@
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>23</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
       <c r="I2" s="7"/>
@@ -1156,21 +1166,21 @@
       <c r="L2" s="9"/>
       <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:13" s="4" customFormat="1" ht="57" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" s="4" customFormat="1" ht="43" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7">
         <v>2025</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -1181,21 +1191,21 @@
       <c r="L3" s="9"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" s="4" customFormat="1" ht="38" x14ac:dyDescent="0.25">
       <c r="A4" s="7">
         <v>2025</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -1206,20 +1216,22 @@
       <c r="L4" s="9"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" s="4" customFormat="1" ht="76" x14ac:dyDescent="0.25">
       <c r="A5" s="7">
         <v>2025</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="7"/>
+        <v>16</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="8"/>
@@ -1227,22 +1239,23 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="9"/>
+      <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" ht="38" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
         <v>2025</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
@@ -1252,120 +1265,95 @@
       <c r="K6" s="7"/>
       <c r="L6" s="9"/>
     </row>
-    <row r="7" spans="1:13" ht="38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="57" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2025</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="9"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="11"/>
     </row>
-    <row r="8" spans="1:13" ht="38" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="76" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2025</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="9"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="10"/>
+      <c r="J8" s="10"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="57" x14ac:dyDescent="0.25">
       <c r="A9" s="7">
         <v>2024</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="76" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
         <v>2024</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+        <v>13</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>2024</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="17" spans="3:3" ht="20" x14ac:dyDescent="0.25">
-      <c r="C17" s="1" t="s">
-        <v>24</v>
+    <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.25">
+      <c r="C15" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
